--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484646_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484646_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.712</v>
+        <v>6.3716</v>
       </c>
       <c r="E2" t="n">
-        <v>4.077</v>
+        <v>3.7614</v>
       </c>
       <c r="F2" t="n">
-        <v>2.635</v>
+        <v>2.6102</v>
       </c>
       <c r="G2" t="n">
         <v>4.4488</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8259</v>
+        <v>0.4855</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1991</v>
+        <v>-0.1165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6267</v>
+        <v>0.602</v>
       </c>
       <c r="V2" t="n">
         <v>-0.945</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0472</v>
+        <v>5.2985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7448</v>
+        <v>0.5253</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3025</v>
+        <v>4.7732</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5131</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4217</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0211</v>
+        <v>-0.2405</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4427</v>
+        <v>0.9134</v>
       </c>
       <c r="V3" t="n">
         <v>3.4894</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3432</v>
+        <v>3.912</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7028</v>
+        <v>1.7314</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6404</v>
+        <v>2.1806</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4593</v>
+        <v>2.6937</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1289</v>
+        <v>1.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3304</v>
+        <v>1.6574</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0278</v>
+        <v>1.9521</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8512</v>
+        <v>1.1921</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1765</v>
+        <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4315</v>
+        <v>0.7416</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2777</v>
+        <v>-0.1558</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1538</v>
+        <v>0.8974</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.3665</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.8326</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.4661</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.9163</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.3823</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.6848</v>
+        <v>-0.0042</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5913</v>
+        <v>-0.299</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0935</v>
+        <v>0.2949</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4583</v>
+        <v>3.8092</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2777</v>
+        <v>2.8754</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1806</v>
+        <v>0.9338</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6937</v>
+        <v>1.5202</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0363</v>
+        <v>1.2571</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6574</v>
+        <v>0.2631</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9521</v>
+        <v>0.7786</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1921</v>
+        <v>1.2847</v>
       </c>
       <c r="L5" t="n">
-        <v>0.76</v>
+        <v>-0.5062</v>
       </c>
       <c r="M5" t="n">
         <v>0.7416</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1558</v>
+        <v>-0.0276</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8974</v>
+        <v>0.7692</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3665</v>
+        <v>2.5656</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4578</v>
+        <v>0.3569</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7526</v>
+        <v>-0.1255</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2949</v>
+        <v>0.4824</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5889</v>
+        <v>-0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9109</v>
+        <v>2.2224</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2258</v>
+        <v>3.629</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6141</v>
+        <v>0.9886</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6117</v>
+        <v>2.6404</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5202</v>
+        <v>2.4593</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2571</v>
+        <v>1.1289</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2631</v>
+        <v>1.3304</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7786</v>
+        <v>1.0278</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2847</v>
+        <v>0.8512</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5062</v>
+        <v>0.1765</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7416</v>
+        <v>1.4315</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0276</v>
+        <v>0.2777</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7692</v>
+        <v>1.1538</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5656</v>
+        <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2265</v>
+        <v>0.9706</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3869</v>
+        <v>0.8771</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1604</v>
+        <v>0.0935</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6335</v>
+        <v>-1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8559</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1539</v>
+        <v>2.916</v>
       </c>
       <c r="E7" t="n">
-        <v>1.053</v>
+        <v>-1.4482</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1009</v>
+        <v>4.3643</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3225</v>
+        <v>-0.011</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.011</v>
+        <v>0.5686</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3336</v>
+        <v>-0.5797</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7792</v>
+        <v>-1.354</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0867</v>
+        <v>0.5077</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6925</v>
+        <v>-1.8617</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5433</v>
+        <v>1.343</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0977</v>
+        <v>0.0609</v>
       </c>
       <c r="O7" t="n">
-        <v>0.641</v>
+        <v>1.2821</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>2.3823</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0849</v>
+        <v>0.5447</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2738</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3587</v>
+        <v>0.6389</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0292</v>
+        <v>2.4538</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6571</v>
+        <v>1.2042</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6863</v>
+        <v>1.2495</v>
       </c>
       <c r="G8" t="n">
+        <v>1.3225</v>
+      </c>
+      <c r="H8" t="n">
         <v>-0.011</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.5686</v>
-      </c>
       <c r="I8" t="n">
-        <v>-0.5797</v>
+        <v>1.3336</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.354</v>
+        <v>0.7792</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5077</v>
+        <v>0.0867</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8617</v>
+        <v>0.6925</v>
       </c>
       <c r="M8" t="n">
-        <v>1.343</v>
+        <v>0.5433</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0609</v>
+        <v>-0.0977</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2821</v>
+        <v>0.641</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3823</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3823</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3422</v>
+        <v>0.2149</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3031</v>
+        <v>0.425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.961</v>
+        <v>-0.21</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9446</v>
+        <v>1.5954</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3711</v>
+        <v>-0.3982</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3156</v>
+        <v>1.9936</v>
       </c>
       <c r="G9" t="n">
         <v>1.6402</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7204</v>
+        <v>0.3712</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4419</v>
+        <v>-0.4691</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1623</v>
+        <v>0.8403</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9658</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6733</v>
+        <v>0.4177</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9713</v>
+        <v>-3.0535</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6447</v>
+        <v>3.4713</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5564</v>
@@ -1234,13 +1234,13 @@
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8919</v>
+        <v>0.6363</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5649</v>
+        <v>0.4827</v>
       </c>
       <c r="U10" t="n">
-        <v>0.327</v>
+        <v>0.1536</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3115</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>I. BOU MINARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2164</v>
+        <v>-0.8928</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4348</v>
+        <v>-2.0357</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2184</v>
+        <v>1.1429</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8976</v>
+        <v>-1.4882</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3816</v>
+        <v>-1.2318</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.516</v>
+        <v>-0.2564</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3524</v>
+        <v>-1.8147</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1954</v>
+        <v>-1.1737</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.157</v>
+        <v>-0.641</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4548</v>
+        <v>0.3265</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1863</v>
+        <v>-0.0581</v>
       </c>
       <c r="O11" t="n">
-        <v>0.641</v>
+        <v>0.3846</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0456</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2187</v>
+        <v>-0.221</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1527</v>
+        <v>0.2666</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. BOU MINARRO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3269</v>
+        <v>-1.3651</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4203</v>
+        <v>-2.4348</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0934</v>
+        <v>1.0697</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4882</v>
+        <v>-1.8976</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2318</v>
+        <v>-1.3816</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2564</v>
+        <v>-0.516</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8147</v>
+        <v>-2.3524</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1737</v>
+        <v>-1.1954</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.641</v>
+        <v>-1.157</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3265</v>
+        <v>0.4548</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0581</v>
+        <v>-0.1863</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3846</v>
+        <v>0.641</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3885</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6056</v>
+        <v>0.2187</v>
       </c>
       <c r="U12" t="n">
-        <v>0.217</v>
+        <v>-0.3013</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>27.0442</v>
+        <v>28.1453</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6148000000000007</v>
+        <v>1.715899999999999</v>
       </c>
       <c r="F13" t="n">
         <v>26.4295</v>
@@ -1438,7 +1438,7 @@
         <v>2.3657</v>
       </c>
       <c r="I13" t="n">
-        <v>6.252699999999999</v>
+        <v>6.2527</v>
       </c>
       <c r="J13" t="n">
         <v>-1.8046</v>
@@ -1468,13 +1468,13 @@
         <v>19.242</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1109</v>
+        <v>4.2118</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6634</v>
+        <v>0.4377</v>
       </c>
       <c r="U13" t="n">
-        <v>3.7741</v>
+        <v>3.774300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.6543999999999999</v>
@@ -1483,7 +1483,7 @@
         <v>7.664400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.009899999999999</v>
+        <v>-7.0099</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0575</v>
+        <v>1.0139</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0562</v>
+        <v>0.8639</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0014</v>
+        <v>0.15</v>
       </c>
       <c r="G14" t="n">
         <v>0.3989</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3367</v>
+        <v>0.293</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3658</v>
+        <v>0.1735</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0291</v>
+        <v>0.1195</v>
       </c>
       <c r="V14" t="n">
         <v>0.3219</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>B. BREM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.178</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3932</v>
+        <v>0.1165</v>
       </c>
       <c r="F16" t="n">
-        <v>1.31</v>
+        <v>-0.2945</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6103</v>
+        <v>-0.3337</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1932</v>
+        <v>-0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.417</v>
+        <v>-0.2885</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.66</v>
+        <v>0.0433</v>
       </c>
       <c r="K16" t="n">
-        <v>0.622</v>
+        <v>0.0433</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2821</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0498</v>
+        <v>-0.3771</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8152</v>
+        <v>-0.0885</v>
       </c>
       <c r="O16" t="n">
-        <v>0.865</v>
+        <v>-0.2885</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.755</v>
+        <v>0.1557</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4608</v>
+        <v>0.0732</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2157</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. BREM</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2275</v>
+        <v>-0.3887</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1165</v>
+        <v>-0.9232</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.344</v>
+        <v>0.5345</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3337</v>
+        <v>2.4308</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0452</v>
+        <v>2.1744</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2885</v>
+        <v>0.2564</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0433</v>
+        <v>1.1763</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0433</v>
+        <v>2.4584</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.2821</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3771</v>
+        <v>1.2545</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0885</v>
+        <v>-0.284</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2885</v>
+        <v>1.5385</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1062</v>
+        <v>-0.398</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0732</v>
+        <v>-0.267</v>
       </c>
       <c r="U17" t="n">
-        <v>0.033</v>
+        <v>-0.1311</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7544</v>
+        <v>-0.5713</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1155</v>
+        <v>-1.4893</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3611</v>
+        <v>0.918</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4308</v>
+        <v>-0.6103</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1744</v>
+        <v>-0.1932</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2564</v>
+        <v>-0.417</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1763</v>
+        <v>-0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4584</v>
+        <v>0.622</v>
       </c>
       <c r="L18" t="n">
         <v>-1.2821</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2545</v>
+        <v>0.0498</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.284</v>
+        <v>-0.8152</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5385</v>
+        <v>0.865</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4661</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
         <v>0.3665</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7637</v>
+        <v>0.2668</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4593</v>
+        <v>-0.5569</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3045</v>
+        <v>0.8237</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9554</v>
+        <v>0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9554</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5797</v>
+        <v>-0.6646</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4178</v>
+        <v>-1.2254</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1619</v>
+        <v>0.5608</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9777</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1805</v>
+        <v>-0.2655</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7715</v>
+        <v>-0.5792</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4091</v>
+        <v>0.3137</v>
       </c>
       <c r="V19" t="n">
         <v>0.945</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0686</v>
+        <v>-1.7234</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5231</v>
+        <v>-2.3308</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4545</v>
+        <v>0.6075</v>
       </c>
       <c r="G20" t="n">
         <v>0.3439</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8078</v>
+        <v>-0.4625</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5324</v>
+        <v>-0.3401</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2754</v>
+        <v>-0.1224</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3662</v>
+        <v>-2.889</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3839</v>
+        <v>-3.6331</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9823</v>
+        <v>0.7441</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0696</v>
+        <v>-2.5286</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6847</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3849</v>
+        <v>-3.1733</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4495</v>
+        <v>-3.3509</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4495</v>
+        <v>0.4952</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-3.8462</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6201</v>
+        <v>0.8223</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2351</v>
+        <v>0.1495</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3849</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3823</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5175999999999999</v>
+        <v>-0.3158</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2255</v>
+        <v>-0.6433</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7079</v>
+        <v>0.3275</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5681</v>
+        <v>0.3219</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5889</v>
+        <v>1.2774</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0208</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.377</v>
+        <v>-3.2185</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0177</v>
+        <v>-2.5378</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6407</v>
+        <v>-0.6807</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5286</v>
+        <v>-2.0696</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6447000000000001</v>
+        <v>-1.6847</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1733</v>
+        <v>-0.3849</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3509</v>
+        <v>-1.4495</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4952</v>
+        <v>-1.4495</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.8462</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8223</v>
+        <v>-0.6201</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1495</v>
+        <v>-0.2351</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.3849</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.3346</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0279</v>
+        <v>0.0717</v>
       </c>
       <c r="U22" t="n">
-        <v>0.224</v>
+        <v>-0.4063</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3219</v>
+        <v>1.5681</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2774</v>
+        <v>1.5889</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9554</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5074</v>
+        <v>-3.9917</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0448</v>
+        <v>-2.7564</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4626</v>
+        <v>-1.2353</v>
       </c>
       <c r="G23" t="n">
         <v>-1.566</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9415</v>
+        <v>-0.4257</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6606</v>
+        <v>-0.3722</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2809</v>
+        <v>-0.0536</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.094</v>
+        <v>-5.2806</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2282</v>
+        <v>-4.3243</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8658</v>
+        <v>-0.9562</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8644</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1918</v>
+        <v>0.0053</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5528</v>
+        <v>-0.6489</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7446</v>
+        <v>0.6542</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5889</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.0189</v>
+        <v>-8.845599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.453200000000001</v>
+        <v>-9.1647</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4343</v>
+        <v>0.3191</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8172</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5208</v>
+        <v>-0.3475</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9736</v>
+        <v>-0.6851</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4528</v>
+        <v>0.3376</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-27.044</v>
+        <v>-25.7622</v>
       </c>
       <c r="E26" t="n">
-        <v>-26.4294</v>
+        <v>-26.4293</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6145999999999997</v>
+        <v>0.6673000000000002</v>
       </c>
       <c r="G26" t="n">
         <v>-8.618599999999999</v>
@@ -2452,7 +2452,7 @@
         <v>-2.3658</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.2527</v>
+        <v>-6.252699999999999</v>
       </c>
       <c r="J26" t="n">
         <v>-10.423</v>
@@ -2482,22 +2482,22 @@
         <v>4.581499999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.1109</v>
+        <v>-1.8288</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.7744</v>
+        <v>-3.7743</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6632000000000002</v>
+        <v>1.9454</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6544000000000001</v>
+        <v>-0.6543999999999996</v>
       </c>
       <c r="W26" t="n">
         <v>7.0098</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.664199999999999</v>
+        <v>-7.664200000000001</v>
       </c>
     </row>
   </sheetData>
